--- a/docs/salary-tax-template-apis.xlsx
+++ b/docs/salary-tax-template-apis.xlsx
@@ -317,9 +317,6 @@
     <x:col min="3" max="3" width="15.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="15.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="15.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="15.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="19.3799991607666" hidden="0" customWidth="1"/>
@@ -328,82 +325,129 @@
     <x:col min="11" max="11" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="15.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="20.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="15.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="27.5" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="27.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>TIN</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>Tax Year</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
-        <x:v>Filing Type</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>Filing Period</x:v>
-      </x:c>
-      <x:c r="E1" s="6" t="str">
-        <x:v>Input Date</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="str">
-        <x:v>Total Salaries &amp; Wages (Cash)</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>Other Fringe Benefits</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>Total Taxable Amount</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>Tax Exempt Amount</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>Tax Amount</x:v>
-      </x:c>
-      <x:c r="K1" s="6" t="str">
-        <x:v>Adjustment Amount</x:v>
-      </x:c>
-      <x:c r="L1" s="6" t="str">
-        <x:v>Carryforward Amount</x:v>
-      </x:c>
-      <x:c r="M1" s="6" t="str">
-        <x:v>Total Amount Due</x:v>
-      </x:c>
-      <x:c r="N1" s="3" t="str">
-        <x:v>Provision Number</x:v>
-      </x:c>
-      <x:c r="O1" s="9" t="str">
-        <x:v>Use User Fallback?</x:v>
-      </x:c>
-      <x:c r="P1" s="9" t="str">
-        <x:v>User Benchmark Rate</x:v>
-      </x:c>
-      <x:c r="Q1" s="9" t="str">
-        <x:v>User TE</x:v>
-      </x:c>
-      <x:c r="R1" s="9" t="str">
-        <x:v>User Fallback Reason</x:v>
-      </x:c>
-      <x:c r="S1" s="9" t="str">
-        <x:v>User Comment</x:v>
+      <x:c r="A1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>TIN</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Tax Year</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Filing Type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Filing Period</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Input Date</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Total Salaries &amp; Wages (Cash)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Other Fringe Benefits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Total Taxable Amount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Tax Exempt Amount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Tax Amount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Adjustment Amount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Carryforward Amount</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="6" t="inlineStr">
+        <x:is>
+          <x:t>Total Amount Due</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" s="3" t="inlineStr">
+        <x:is>
+          <x:t>Provision Number</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback?</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>User TE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback Reason</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S1" s="9" t="inlineStr">
+        <x:is>
+          <x:t>User Comment</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="18" t="str">
-        <x:v>TIN-XXXXX</x:v>
+      <x:c r="A2" s="18" t="inlineStr">
+        <x:is>
+          <x:t>TIN-XXXXX</x:t>
+        </x:is>
       </x:c>
       <x:c r="B2" s="19" t="n">
         <x:v>2026</x:v>
       </x:c>
-      <x:c r="C2" s="18" t="str">
-        <x:v>Monthly</x:v>
-      </x:c>
-      <x:c r="D2" s="18" t="str">
-        <x:v>05/2026</x:v>
+      <x:c r="C2" s="18" t="inlineStr">
+        <x:is>
+          <x:t>Monthly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="18" t="inlineStr">
+        <x:is>
+          <x:t>05/2026</x:t>
+        </x:is>
       </x:c>
       <x:c r="E2" s="20"/>
       <x:c r="F2" s="21" t="n">
@@ -430,16 +474,20 @@
       <x:c r="M2" s="21" t="n">
         <x:v>4500000</x:v>
       </x:c>
-      <x:c r="N2" s="18" t="str">
-        <x:v>T21</x:v>
-      </x:c>
-      <x:c r="O2" s="18" t="str">
-        <x:v>No</x:v>
+      <x:c r="N2" s="18" t="inlineStr">
+        <x:is>
+          <x:t>T21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O2" s="18" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
       </x:c>
       <x:c r="P2" s="22"/>
       <x:c r="Q2" s="21"/>
-      <x:c r="R2" s="18" t="str"/>
-      <x:c r="S2" s="18" t="str"/>
+      <x:c r="R2" s="18"/>
+      <x:c r="S2" s="18"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5"/>
@@ -21421,7 +21469,6 @@
       <x:c r="S1001" s="11"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:dataValidations count="6">
     <x:dataValidation type="whole" operator="between" allowBlank="1" showErrorMessage="1" sqref="B2:B1001">
       <x:formula1>2000</x:formula1>
@@ -21443,6 +21490,7 @@
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -21457,207 +21505,299 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="27" t="str">
-        <x:v>Salary Tax Import Template - Instructions</x:v>
+      <x:c r="A1" s="27" t="inlineStr">
+        <x:is>
+          <x:t>Salary Tax Import Template - Instructions</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="30" t="str">
-        <x:v>Information Type</x:v>
-      </x:c>
-      <x:c r="B3" s="30" t="str">
-        <x:v>Color</x:v>
-      </x:c>
-      <x:c r="C3" s="30" t="str">
-        <x:v>Meaning</x:v>
-      </x:c>
-      <x:c r="D3" s="30" t="str">
-        <x:v>Examples</x:v>
+      <x:c r="A3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Information Type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Color</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Meaning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Examples</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="5" t="str">
-        <x:v>Primary Required</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="str">
-        <x:v>Dark blue header, light blue input cells</x:v>
-      </x:c>
-      <x:c r="C4" s="5" t="str">
-        <x:v>Required for normal salary TE calculation.</x:v>
-      </x:c>
-      <x:c r="D4" s="5" t="str">
-        <x:v>TIN, Tax Year, Filing Period, Tax Exempt Amount, Tax Amount, Provision Number</x:v>
+      <x:c r="A4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Primary Required</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue header, light blue input cells</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>Required for normal salary TE calculation.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="5" t="inlineStr">
+        <x:is>
+          <x:t>TIN, Tax Year, Filing Period, Tax Exempt Amount, Tax Amount, Provision Number</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="8" t="str">
-        <x:v>Primary Optional</x:v>
-      </x:c>
-      <x:c r="B5" s="8" t="str">
-        <x:v>Slate/gray-blue header, white input cells</x:v>
-      </x:c>
-      <x:c r="C5" s="8" t="str">
-        <x:v>Official/supporting filing information. Useful for audit, but not directly used by the current TE formula.</x:v>
-      </x:c>
-      <x:c r="D5" s="8" t="str">
-        <x:v>Filing Type, Input Date, Total Salaries, Total Taxable Amount, Total Amount Due</x:v>
+      <x:c r="A5" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Primary Optional</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Slate/gray-blue header, white input cells</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Official/supporting filing information. Useful for audit, but not directly used by the current TE formula.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="8" t="inlineStr">
+        <x:is>
+          <x:t>Filing Type, Input Date, Total Salaries, Total Taxable Amount, Total Amount Due</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>User Fallback</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>Orange header, light amber input cells</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>Optional user-provided benchmark or TE values used only when system inputs are incomplete or special judgement is required.</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>User Benchmark Rate, User TE, User Fallback Reason</x:v>
+      <x:c r="A6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>User Fallback</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>Orange header, light amber input cells</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>Optional user-provided benchmark or TE values used only when system inputs are incomplete or special judgement is required.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="11" t="inlineStr">
+        <x:is>
+          <x:t>User Benchmark Rate, User TE, User Fallback Reason</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="28" t="str">
-        <x:v>Protected Reference Sheets</x:v>
-      </x:c>
-      <x:c r="B7" s="28" t="str">
-        <x:v>Dark blue headers</x:v>
-      </x:c>
-      <x:c r="C7" s="28" t="str">
-        <x:v>Instructions, Validation Lists, and Data Dictionary are read-only to avoid accidental reference changes.</x:v>
-      </x:c>
-      <x:c r="D7" s="28" t="str">
-        <x:v>Use Salary Import for data entry.</x:v>
+      <x:c r="A7" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Protected Reference Sheets</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Dark blue headers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Instructions, Validation Lists, and Data Dictionary are read-only to avoid accidental reference changes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use Salary Import for data entry.</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="28" t="str"/>
-      <x:c r="B8" s="28" t="str"/>
-      <x:c r="C8" s="28" t="str"/>
-      <x:c r="D8" s="28" t="str"/>
+      <x:c r="A8" s="28"/>
+      <x:c r="B8" s="28"/>
+      <x:c r="C8" s="28"/>
+      <x:c r="D8" s="28"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="28" t="str">
-        <x:v>Rule</x:v>
-      </x:c>
-      <x:c r="B9" s="28" t="str">
-        <x:v>Description</x:v>
-      </x:c>
-      <x:c r="C9" s="28" t="str"/>
-      <x:c r="D9" s="28" t="str"/>
+      <x:c r="A9" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="28"/>
+      <x:c r="D9" s="28"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="30" t="str">
-        <x:v>Current compatibility</x:v>
-      </x:c>
-      <x:c r="B10" s="30" t="str">
-        <x:v>Columns A:N match the current Salary Tax importer. The importer ignores fallback columns O:S until import_salary.php is updated.</x:v>
-      </x:c>
-      <x:c r="C10" s="30" t="str"/>
-      <x:c r="D10" s="30" t="str"/>
+      <x:c r="A10" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Current compatibility</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="30" t="inlineStr">
+        <x:is>
+          <x:t>Columns A:N match the current Salary Tax importer. The importer ignores fallback columns O:S until import_salary.php is updated.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="30"/>
+      <x:c r="D10" s="30"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="28" t="str">
-        <x:v>Use primary first</x:v>
-      </x:c>
-      <x:c r="B11" s="28" t="str">
-        <x:v>The current engine calculates TE from Tax Exempt Amount multiplied by the configured benchmark rate for the Provision Number.</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="str"/>
-      <x:c r="D11" s="28" t="str"/>
+      <x:c r="A11" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use primary first</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="28" t="inlineStr">
+        <x:is>
+          <x:t>The current engine calculates TE from Tax Exempt Amount multiplied by the configured benchmark rate for the Provision Number.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="28"/>
+      <x:c r="D11" s="28"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="28" t="str">
-        <x:v>Keep official totals</x:v>
-      </x:c>
-      <x:c r="B12" s="28" t="str">
-        <x:v>Total Taxable Amount and Total Amount Due may be derived, but should remain as reported audit fields.</x:v>
-      </x:c>
-      <x:c r="C12" s="28" t="str"/>
-      <x:c r="D12" s="28" t="str"/>
+      <x:c r="A12" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Keep official totals</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Total Taxable Amount and Total Amount Due may be derived, but should remain as reported audit fields.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="28"/>
+      <x:c r="D12" s="28"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="28" t="str">
-        <x:v>Fallback rule</x:v>
-      </x:c>
-      <x:c r="B13" s="28" t="str">
-        <x:v>Use User Fallback only when normal system calculation is not sufficient or the expert/user has an agreed alternative value.</x:v>
-      </x:c>
-      <x:c r="C13" s="28" t="str"/>
-      <x:c r="D13" s="28" t="str"/>
+      <x:c r="A13" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Fallback rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use User Fallback only when normal system calculation is not sufficient or the expert/user has an agreed alternative value.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="28"/>
+      <x:c r="D13" s="28"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="28" t="str">
-        <x:v>Fallback reason</x:v>
-      </x:c>
-      <x:c r="B14" s="28" t="str">
-        <x:v>Required when Use User Fallback? is Yes.</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="str"/>
-      <x:c r="D14" s="28" t="str"/>
+      <x:c r="A14" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Fallback reason</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Required when Use User Fallback? is Yes.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="28"/>
+      <x:c r="D14" s="28"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="28" t="str">
-        <x:v>Dropdown fields</x:v>
-      </x:c>
-      <x:c r="B15" s="28" t="str">
-        <x:v>Use dropdowns for Filing Type, Provision Number, Use User Fallback?, and User Fallback Reason.</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="str"/>
-      <x:c r="D15" s="28" t="str"/>
+      <x:c r="A15" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Dropdown fields</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Use dropdowns for Filing Type, Provision Number, Use User Fallback?, and User Fallback Reason.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="28"/>
+      <x:c r="D15" s="28"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="28" t="str">
-        <x:v>No simple Excel calculations</x:v>
-      </x:c>
-      <x:c r="B16" s="28" t="str">
-        <x:v>Do not add calculated benchmark or TE columns. Keep raw official filing values plus controlled fallback fields.</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="str"/>
-      <x:c r="D16" s="28" t="str"/>
+      <x:c r="A16" s="28" t="inlineStr">
+        <x:is>
+          <x:t>No simple Excel calculations</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Do not add calculated benchmark or TE columns. Keep raw official filing values plus controlled fallback fields.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="28"/>
+      <x:c r="D16" s="28"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="28" t="str">
-        <x:v>Mandatory fields</x:v>
-      </x:c>
-      <x:c r="B17" s="28" t="str">
-        <x:v>TIN, Tax Year, Filing Period, Tax Exempt Amount, Tax Amount, and Provision Number.</x:v>
-      </x:c>
-      <x:c r="C17" s="28" t="str"/>
-      <x:c r="D17" s="28" t="str"/>
+      <x:c r="A17" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Mandatory fields</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="28" t="inlineStr">
+        <x:is>
+          <x:t>TIN, Tax Year, Filing Period, Tax Exempt Amount, Tax Amount, and Provision Number.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="28"/>
+      <x:c r="D17" s="28"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="28" t="str">
-        <x:v>Template version</x:v>
-      </x:c>
-      <x:c r="B18" s="28" t="str">
-        <x:v>SALARY_IMPORT v1.0</x:v>
-      </x:c>
-      <x:c r="C18" s="28" t="str"/>
-      <x:c r="D18" s="28" t="str"/>
+      <x:c r="A18" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Template version</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="28" t="inlineStr">
+        <x:is>
+          <x:t>SALARY_IMPORT v1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="28"/>
+      <x:c r="D18" s="28"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="28" t="str">
-        <x:v>Protection password</x:v>
-      </x:c>
-      <x:c r="B19" s="28" t="str">
-        <x:v>TaxETS2026</x:v>
-      </x:c>
-      <x:c r="C19" s="28" t="str">
-        <x:v>Used only to prevent accidental edits to read-only sheets.</x:v>
-      </x:c>
-      <x:c r="D19" s="28" t="str"/>
+      <x:c r="A19" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Protection password</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="28" t="inlineStr">
+        <x:is>
+          <x:t>TaxETS2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Used only to prevent accidental edits to read-only sheets.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="28"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="28" t="str">
-        <x:v>Import code note</x:v>
-      </x:c>
-      <x:c r="B20" s="28" t="str">
-        <x:v>After agreement, import_salary.php can be updated to read fallback columns O:S and apply the same hybrid principle as other tax types.</x:v>
-      </x:c>
-      <x:c r="C20" s="28" t="str"/>
-      <x:c r="D20" s="28" t="str"/>
+      <x:c r="A20" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Import code note</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="28" t="inlineStr">
+        <x:is>
+          <x:t>After agreement, import_salary.php can be updated to read fallback columns O:S and apply the same hybrid principle as other tax types.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="28"/>
+      <x:c r="D20" s="28"/>
     </x:row>
   </x:sheetData>
   <x:sheetProtection password="C3BC" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -21679,330 +21819,524 @@
     <x:col min="9" max="9" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="53.75" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="18.75" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="53.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="str">
-        <x:v>Filing Type</x:v>
-      </x:c>
-      <x:c r="B1" s="24" t="str"/>
-      <x:c r="C1" s="24" t="str">
-        <x:v>Provision Number</x:v>
-      </x:c>
-      <x:c r="D1" s="24" t="str"/>
-      <x:c r="E1" s="24" t="str">
-        <x:v>Yes/No</x:v>
-      </x:c>
-      <x:c r="F1" s="24" t="str"/>
-      <x:c r="G1" s="24" t="str">
-        <x:v>Fallback Reason</x:v>
+      <x:c r="A1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Filing Type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="24"/>
+      <x:c r="C1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Provision Number</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="24"/>
+      <x:c r="E1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Yes/No</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="24"/>
+      <x:c r="G1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Fallback Reason</x:t>
+        </x:is>
       </x:c>
       <x:c r="H1" s="24"/>
-      <x:c r="I1" s="24" t="str">
-        <x:v>Provision</x:v>
-      </x:c>
-      <x:c r="J1" s="24" t="str">
-        <x:v>Legal Basis</x:v>
-      </x:c>
-      <x:c r="K1" s="24" t="str">
-        <x:v>Type</x:v>
-      </x:c>
-      <x:c r="L1" s="24" t="str">
-        <x:v>Description</x:v>
-      </x:c>
-      <x:c r="M1" s="24" t="str">
-        <x:v>Purpose</x:v>
-      </x:c>
-      <x:c r="N1" s="24" t="str">
-        <x:v>Benchmark Rate %</x:v>
+      <x:c r="I1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Provision</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Legal Basis</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Purpose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" s="24" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark Rate %</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>Monthly</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>T21</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="G2" t="str"/>
-      <x:c r="I2" t="str">
-        <x:v>T21</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>PIT Law Art. 22</x:v>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>Personal Allowance / Base Exemption</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>Basic personal exemption for individual taxpayers</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>Monthly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t>T21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t>No</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2"/>
+      <x:c r="I2" t="inlineStr">
+        <x:is>
+          <x:t>T21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K2" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>Personal Allowance / Base Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M2" t="inlineStr">
+        <x:is>
+          <x:t>Basic personal exemption for individual taxpayers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N2" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>Yearly</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>T22</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>Missing benchmark rate</x:v>
-      </x:c>
-      <x:c r="I3" t="str">
-        <x:v>T22</x:v>
-      </x:c>
-      <x:c r="J3" t="str">
-        <x:v>PIT Law Art. 23</x:v>
-      </x:c>
-      <x:c r="K3" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="L3" t="str">
-        <x:v>Spouse Allowance</x:v>
-      </x:c>
-      <x:c r="M3" t="str">
-        <x:v>Deduction for married taxpayers with non-earning spouse</x:v>
-      </x:c>
-      <x:c r="N3" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t>Yearly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t>T22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t>Yes</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" t="inlineStr">
+        <x:is>
+          <x:t>Missing benchmark rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I3" t="inlineStr">
+        <x:is>
+          <x:t>T22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J3" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K3" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L3" t="inlineStr">
+        <x:is>
+          <x:t>Spouse Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M3" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for married taxpayers with non-earning spouse</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N3" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="C4" t="str">
-        <x:v>T23</x:v>
-      </x:c>
-      <x:c r="G4" t="str">
-        <x:v>Unclear provision number</x:v>
-      </x:c>
-      <x:c r="I4" t="str">
-        <x:v>T23</x:v>
-      </x:c>
-      <x:c r="J4" t="str">
-        <x:v>PIT Law Art. 24</x:v>
-      </x:c>
-      <x:c r="K4" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="L4" t="str">
-        <x:v>Child / Educational Allowance</x:v>
-      </x:c>
-      <x:c r="M4" t="str">
-        <x:v>Deduction for dependent children under 18 or in education</x:v>
-      </x:c>
-      <x:c r="N4" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t>T23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" t="inlineStr">
+        <x:is>
+          <x:t>Unclear provision number</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I4" t="inlineStr">
+        <x:is>
+          <x:t>T23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J4" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 24</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K4" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L4" t="inlineStr">
+        <x:is>
+          <x:t>Child / Educational Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M4" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for dependent children under 18 or in education</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N4" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="C5" t="str">
-        <x:v>T24</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>Multiple provisions</x:v>
-      </x:c>
-      <x:c r="I5" t="str">
-        <x:v>T24</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>PIT Law Art. 25</x:v>
-      </x:c>
-      <x:c r="K5" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="L5" t="str">
-        <x:v>Senior / Elderly Allowance</x:v>
-      </x:c>
-      <x:c r="M5" t="str">
-        <x:v>Additional exemption for taxpayers aged 60+</x:v>
-      </x:c>
-      <x:c r="N5" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t>T24</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" t="inlineStr">
+        <x:is>
+          <x:t>Multiple provisions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I5" t="inlineStr">
+        <x:is>
+          <x:t>T24</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J5" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 25</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K5" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L5" t="inlineStr">
+        <x:is>
+          <x:t>Senior / Elderly Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M5" t="inlineStr">
+        <x:is>
+          <x:t>Additional exemption for taxpayers aged 60+</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N5" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="C6" t="str">
-        <x:v>T25</x:v>
-      </x:c>
-      <x:c r="G6" t="str">
-        <x:v>Special legal treatment</x:v>
-      </x:c>
-      <x:c r="I6" t="str">
-        <x:v>T25</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>PIT Law Art. 26</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="L6" t="str">
-        <x:v>Disability Allowance</x:v>
-      </x:c>
-      <x:c r="M6" t="str">
-        <x:v>Exemption for persons with disabilities</x:v>
-      </x:c>
-      <x:c r="N6" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t>T25</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" t="inlineStr">
+        <x:is>
+          <x:t>Special legal treatment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I6" t="inlineStr">
+        <x:is>
+          <x:t>T25</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J6" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K6" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L6" t="inlineStr">
+        <x:is>
+          <x:t>Disability Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M6" t="inlineStr">
+        <x:is>
+          <x:t>Exemption for persons with disabilities</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N6" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="C7" t="str">
-        <x:v>T26</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>Legacy assessment</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>T26</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>PIT Law Art. 27</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="L7" t="str">
-        <x:v>Insurance Premium Deduction</x:v>
-      </x:c>
-      <x:c r="M7" t="str">
-        <x:v>Deduction for insurance premiums paid</x:v>
-      </x:c>
-      <x:c r="N7" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t>T26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" t="inlineStr">
+        <x:is>
+          <x:t>Legacy assessment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" t="inlineStr">
+        <x:is>
+          <x:t>T26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L7" t="inlineStr">
+        <x:is>
+          <x:t>Insurance Premium Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M7" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for insurance premiums paid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N7" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="C8" t="str">
-        <x:v>T27</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
-        <x:v>User judgment</x:v>
-      </x:c>
-      <x:c r="I8" t="str">
-        <x:v>T27</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
-        <x:v>PIT Law Art. 28</x:v>
-      </x:c>
-      <x:c r="K8" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="L8" t="str">
-        <x:v>Life Insurance</x:v>
-      </x:c>
-      <x:c r="M8" t="str">
-        <x:v>Deduction for life insurance premiums</x:v>
-      </x:c>
-      <x:c r="N8" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>T27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" t="inlineStr">
+        <x:is>
+          <x:t>User judgment</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" t="inlineStr">
+        <x:is>
+          <x:t>T27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J8" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 28</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K8" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L8" t="inlineStr">
+        <x:is>
+          <x:t>Life Insurance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M8" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for life insurance premiums</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N8" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="C9" t="str">
-        <x:v>T28</x:v>
-      </x:c>
-      <x:c r="G9" t="str">
-        <x:v>Other</x:v>
-      </x:c>
-      <x:c r="I9" t="str">
-        <x:v>T28</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>PIT Law Art. 29</x:v>
-      </x:c>
-      <x:c r="K9" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="L9" t="str">
-        <x:v>Housing Interest Deduction</x:v>
-      </x:c>
-      <x:c r="M9" t="str">
-        <x:v>Deduction for housing loan interest</x:v>
-      </x:c>
-      <x:c r="N9" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>T28</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" t="inlineStr">
+        <x:is>
+          <x:t>Other</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" t="inlineStr">
+        <x:is>
+          <x:t>T28</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 29</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L9" t="inlineStr">
+        <x:is>
+          <x:t>Housing Interest Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M9" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for housing loan interest</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N9" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="C10" t="str">
-        <x:v>T29</x:v>
-      </x:c>
-      <x:c r="I10" t="str">
-        <x:v>T29</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
-        <x:v>PIT Law Art. 30</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="L10" t="str">
-        <x:v>Social Security Contribution</x:v>
-      </x:c>
-      <x:c r="M10" t="str">
-        <x:v>Deduction for mandatory social security contributions</x:v>
-      </x:c>
-      <x:c r="N10" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t>T29</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" t="inlineStr">
+        <x:is>
+          <x:t>T29</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K10" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L10" t="inlineStr">
+        <x:is>
+          <x:t>Social Security Contribution</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M10" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for mandatory social security contributions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N10" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="C11" t="str">
-        <x:v>T30</x:v>
-      </x:c>
-      <x:c r="I11" t="str">
-        <x:v>T30</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
-        <x:v>PIT Law Art. 31</x:v>
-      </x:c>
-      <x:c r="K11" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="L11" t="str">
-        <x:v>Other Exemptions</x:v>
-      </x:c>
-      <x:c r="M11" t="str">
-        <x:v>Other tax-exempt income per PIT law</x:v>
-      </x:c>
-      <x:c r="N11" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>T30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" t="inlineStr">
+        <x:is>
+          <x:t>T30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 31</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K11" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L11" t="inlineStr">
+        <x:is>
+          <x:t>Other Exemptions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M11" t="inlineStr">
+        <x:is>
+          <x:t>Other tax-exempt income per PIT law</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N11" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="C12" t="str">
-        <x:v>Multiple</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>Multiple</x:v>
-      </x:c>
-      <x:c r="J12" t="str"/>
-      <x:c r="K12" t="str">
-        <x:v>Default</x:v>
-      </x:c>
-      <x:c r="L12" t="str">
-        <x:v>Multiple/unspecified provisions</x:v>
-      </x:c>
-      <x:c r="M12" t="str">
-        <x:v>Default salary TE calculation</x:v>
-      </x:c>
-      <x:c r="N12" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t>Multiple</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" t="inlineStr">
+        <x:is>
+          <x:t>Multiple</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12" t="inlineStr">
+        <x:is>
+          <x:t>Default</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L12" t="inlineStr">
+        <x:is>
+          <x:t>Multiple/unspecified provisions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M12" t="inlineStr">
+        <x:is>
+          <x:t>Default salary TE calculation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N12" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22018,70 +22352,104 @@
     <x:col min="1" max="1" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17.5" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="17.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="55" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="26" t="str">
-        <x:v>Provision Number</x:v>
-      </x:c>
-      <x:c r="B1" s="26" t="str">
-        <x:v>Legal Basis</x:v>
-      </x:c>
-      <x:c r="C1" s="26" t="str">
-        <x:v>Type</x:v>
-      </x:c>
-      <x:c r="D1" s="26" t="str">
-        <x:v>Description</x:v>
-      </x:c>
-      <x:c r="E1" s="26" t="str">
-        <x:v>Purpose</x:v>
-      </x:c>
-      <x:c r="F1" s="26" t="str">
-        <x:v>Benchmark Rate %</x:v>
+      <x:c r="A1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Provision Number</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Legal Basis</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Type</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Purpose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Benchmark Rate %</x:t>
+        </x:is>
       </x:c>
       <x:c r="G1" s="26"/>
-      <x:c r="H1" s="26" t="str">
-        <x:v>Start Year</x:v>
-      </x:c>
-      <x:c r="I1" s="26" t="str">
-        <x:v>End Year</x:v>
-      </x:c>
-      <x:c r="J1" s="26" t="str">
-        <x:v>Provision Number</x:v>
-      </x:c>
-      <x:c r="K1" s="26" t="str">
-        <x:v>Rate %</x:v>
-      </x:c>
-      <x:c r="L1" s="26" t="str">
-        <x:v>Description</x:v>
+      <x:c r="H1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Start Year</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>End Year</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Provision Number</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Rate %</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="26" t="inlineStr">
+        <x:is>
+          <x:t>Description</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>T21</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>PIT Law Art. 22</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>Personal Allowance / Base Exemption</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>Basic personal exemption for individual taxpayers</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A2" t="inlineStr">
+        <x:is>
+          <x:t>T21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" t="inlineStr">
+        <x:is>
+          <x:t>Personal Allowance / Base Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t>Basic personal exemption for individual taxpayers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H2" t="n">
         <x:v>2020</x:v>
@@ -22089,34 +22457,52 @@
       <x:c r="I2" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J2" t="str">
-        <x:v>Multiple</x:v>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>Default rate for multiple/unspecified provisions</x:v>
+      <x:c r="J2" t="inlineStr">
+        <x:is>
+          <x:t>Multiple</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K2" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>Default rate for multiple/unspecified provisions</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>T22</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>PIT Law Art. 23</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>Spouse Allowance</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>Deduction for married taxpayers with non-earning spouse</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A3" t="inlineStr">
+        <x:is>
+          <x:t>T22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" t="inlineStr">
+        <x:is>
+          <x:t>Spouse Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for married taxpayers with non-earning spouse</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H3" t="n">
         <x:v>2020</x:v>
@@ -22124,34 +22510,52 @@
       <x:c r="I3" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J3" t="str">
-        <x:v>T21</x:v>
-      </x:c>
-      <x:c r="K3" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L3" t="str">
-        <x:v>Personal Allowance - estimated effective rate</x:v>
+      <x:c r="J3" t="inlineStr">
+        <x:is>
+          <x:t>T21</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K3" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L3" t="inlineStr">
+        <x:is>
+          <x:t>Personal Allowance - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
-        <x:v>T23</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>PIT Law Art. 24</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>Child / Educational Allowance</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>Deduction for dependent children under 18 or in education</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A4" t="inlineStr">
+        <x:is>
+          <x:t>T23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 24</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" t="inlineStr">
+        <x:is>
+          <x:t>Child / Educational Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for dependent children under 18 or in education</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H4" t="n">
         <x:v>2020</x:v>
@@ -22159,34 +22563,52 @@
       <x:c r="I4" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J4" t="str">
-        <x:v>T22</x:v>
-      </x:c>
-      <x:c r="K4" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L4" t="str">
-        <x:v>Spouse Allowance - estimated effective rate</x:v>
+      <x:c r="J4" t="inlineStr">
+        <x:is>
+          <x:t>T22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K4" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L4" t="inlineStr">
+        <x:is>
+          <x:t>Spouse Allowance - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
-        <x:v>T24</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>PIT Law Art. 25</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>Senior / Elderly Allowance</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>Additional exemption for taxpayers aged 60+</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A5" t="inlineStr">
+        <x:is>
+          <x:t>T24</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 25</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t>Senior / Elderly Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" t="inlineStr">
+        <x:is>
+          <x:t>Additional exemption for taxpayers aged 60+</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H5" t="n">
         <x:v>2020</x:v>
@@ -22194,34 +22616,52 @@
       <x:c r="I5" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J5" t="str">
-        <x:v>T23</x:v>
-      </x:c>
-      <x:c r="K5" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L5" t="str">
-        <x:v>Child Allowance - estimated effective rate</x:v>
+      <x:c r="J5" t="inlineStr">
+        <x:is>
+          <x:t>T23</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K5" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L5" t="inlineStr">
+        <x:is>
+          <x:t>Child Allowance - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>T25</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>PIT Law Art. 26</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>Disability Allowance</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>Exemption for persons with disabilities</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A6" t="inlineStr">
+        <x:is>
+          <x:t>T25</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" t="inlineStr">
+        <x:is>
+          <x:t>Disability Allowance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" t="inlineStr">
+        <x:is>
+          <x:t>Exemption for persons with disabilities</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H6" t="n">
         <x:v>2020</x:v>
@@ -22229,34 +22669,52 @@
       <x:c r="I6" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J6" t="str">
-        <x:v>T24</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L6" t="str">
-        <x:v>Senior Allowance - estimated effective rate</x:v>
+      <x:c r="J6" t="inlineStr">
+        <x:is>
+          <x:t>T24</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K6" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L6" t="inlineStr">
+        <x:is>
+          <x:t>Senior Allowance - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>T26</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>PIT Law Art. 27</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>Insurance Premium Deduction</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>Deduction for insurance premiums paid</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A7" t="inlineStr">
+        <x:is>
+          <x:t>T26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" t="inlineStr">
+        <x:is>
+          <x:t>Insurance Premium Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for insurance premiums paid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H7" t="n">
         <x:v>2020</x:v>
@@ -22264,34 +22722,52 @@
       <x:c r="I7" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J7" t="str">
-        <x:v>T25</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L7" t="str">
-        <x:v>Disability Allowance - estimated effective rate</x:v>
+      <x:c r="J7" t="inlineStr">
+        <x:is>
+          <x:t>T25</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L7" t="inlineStr">
+        <x:is>
+          <x:t>Disability Allowance - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>T27</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>PIT Law Art. 28</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>Life Insurance</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>Deduction for life insurance premiums</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A8" t="inlineStr">
+        <x:is>
+          <x:t>T27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 28</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" t="inlineStr">
+        <x:is>
+          <x:t>Life Insurance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for life insurance premiums</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H8" t="n">
         <x:v>2020</x:v>
@@ -22299,34 +22775,52 @@
       <x:c r="I8" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J8" t="str">
-        <x:v>T26</x:v>
-      </x:c>
-      <x:c r="K8" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L8" t="str">
-        <x:v>Insurance Premium - estimated effective rate</x:v>
+      <x:c r="J8" t="inlineStr">
+        <x:is>
+          <x:t>T26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K8" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L8" t="inlineStr">
+        <x:is>
+          <x:t>Insurance Premium - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>T28</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>PIT Law Art. 29</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>Housing Interest Deduction</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>Deduction for housing loan interest</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A9" t="inlineStr">
+        <x:is>
+          <x:t>T28</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 29</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" t="inlineStr">
+        <x:is>
+          <x:t>Housing Interest Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for housing loan interest</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H9" t="n">
         <x:v>2020</x:v>
@@ -22334,34 +22828,52 @@
       <x:c r="I9" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J9" t="str">
-        <x:v>T27</x:v>
-      </x:c>
-      <x:c r="K9" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L9" t="str">
-        <x:v>Life Insurance - estimated effective rate</x:v>
+      <x:c r="J9" t="inlineStr">
+        <x:is>
+          <x:t>T27</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L9" t="inlineStr">
+        <x:is>
+          <x:t>Life Insurance - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>T29</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>PIT Law Art. 30</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Deduction</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>Social Security Contribution</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>Deduction for mandatory social security contributions</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>5.00</x:v>
+      <x:c r="A10" t="inlineStr">
+        <x:is>
+          <x:t>T29</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" t="inlineStr">
+        <x:is>
+          <x:t>Deduction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" t="inlineStr">
+        <x:is>
+          <x:t>Social Security Contribution</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" t="inlineStr">
+        <x:is>
+          <x:t>Deduction for mandatory social security contributions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H10" t="n">
         <x:v>2020</x:v>
@@ -22369,34 +22881,52 @@
       <x:c r="I10" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J10" t="str">
-        <x:v>T28</x:v>
-      </x:c>
-      <x:c r="K10" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L10" t="str">
-        <x:v>Housing Interest - estimated effective rate</x:v>
+      <x:c r="J10" t="inlineStr">
+        <x:is>
+          <x:t>T28</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K10" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L10" t="inlineStr">
+        <x:is>
+          <x:t>Housing Interest - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>T30</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>PIT Law Art. 31</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>Exemption</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>Other Exemptions</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>Other tax-exempt income per PIT law</x:v>
-      </x:c>
-      <x:c r="F11" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A11" t="inlineStr">
+        <x:is>
+          <x:t>T30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="inlineStr">
+        <x:is>
+          <x:t>PIT Law Art. 31</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" t="inlineStr">
+        <x:is>
+          <x:t>Exemption</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t>Other Exemptions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" t="inlineStr">
+        <x:is>
+          <x:t>Other tax-exempt income per PIT law</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H11" t="n">
         <x:v>2020</x:v>
@@ -22404,32 +22934,48 @@
       <x:c r="I11" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J11" t="str">
-        <x:v>T29</x:v>
-      </x:c>
-      <x:c r="K11" t="str">
-        <x:v>5.00</x:v>
-      </x:c>
-      <x:c r="L11" t="str">
-        <x:v>Social Security Contribution - reduced rate</x:v>
+      <x:c r="J11" t="inlineStr">
+        <x:is>
+          <x:t>T29</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K11" t="inlineStr">
+        <x:is>
+          <x:t>5.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L11" t="inlineStr">
+        <x:is>
+          <x:t>Social Security Contribution - reduced rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" t="str">
-        <x:v>Multiple</x:v>
-      </x:c>
-      <x:c r="B12" t="str"/>
-      <x:c r="C12" t="str">
-        <x:v>Default</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>Multiple/unspecified provisions</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>Default salary TE calculation</x:v>
-      </x:c>
-      <x:c r="F12" t="str">
-        <x:v>10.00</x:v>
+      <x:c r="A12" t="inlineStr">
+        <x:is>
+          <x:t>Multiple</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12"/>
+      <x:c r="C12" t="inlineStr">
+        <x:is>
+          <x:t>Default</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr">
+        <x:is>
+          <x:t>Multiple/unspecified provisions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" t="inlineStr">
+        <x:is>
+          <x:t>Default salary TE calculation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
       </x:c>
       <x:c r="H12" t="n">
         <x:v>2020</x:v>
@@ -22437,14 +22983,20 @@
       <x:c r="I12" t="n">
         <x:v>2099</x:v>
       </x:c>
-      <x:c r="J12" t="str">
-        <x:v>T30</x:v>
-      </x:c>
-      <x:c r="K12" t="str">
-        <x:v>10.00</x:v>
-      </x:c>
-      <x:c r="L12" t="str">
-        <x:v>Other Exemptions - estimated effective rate</x:v>
+      <x:c r="J12" t="inlineStr">
+        <x:is>
+          <x:t>T30</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" t="inlineStr">
+        <x:is>
+          <x:t>10.00</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L12" t="inlineStr">
+        <x:is>
+          <x:t>Other Exemptions - estimated effective rate</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22464,31 +23016,47 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="31" t="str">
-        <x:v>Version</x:v>
-      </x:c>
-      <x:c r="B1" s="31" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="C1" s="31" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-      <x:c r="D1" s="31" t="str">
-        <x:v>Change</x:v>
+      <x:c r="A1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Version</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Date</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Owner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="31" t="inlineStr">
+        <x:is>
+          <x:t>Change</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="28" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="B2" s="28" t="str">
-        <x:v>2026-06-05</x:v>
-      </x:c>
-      <x:c r="C2" s="28" t="str">
-        <x:v>APIS / Tax-ETS</x:v>
-      </x:c>
-      <x:c r="D2" s="28" t="str">
-        <x:v>Initial recommended Salary Tax template with compatible A:N layout and user fallback columns O:S.</x:v>
+      <x:c r="A2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>2026-06-05</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>APIS / Tax-ETS</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="28" t="inlineStr">
+        <x:is>
+          <x:t>Initial recommended Salary Tax template with compatible A:N layout and user fallback columns O:S.</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
